--- a/measurements/38/Filled_2D_sections/sagittal/week38_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/38/Filled_2D_sections/sagittal/week38_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,62 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +556,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.63355145746579</v>
+        <v>4053.28798185941</v>
       </c>
       <c r="D2" t="n">
-        <v>17.12636095430793</v>
+        <v>334.3718091079167</v>
       </c>
       <c r="E2" t="n">
-        <v>14.18955215593664</v>
+        <v>277.0341135206676</v>
       </c>
       <c r="F2" t="n">
         <v>1.20696980187233</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4555730397483371</v>
+        <v>0.4555730397483372</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5238185975609756</v>
+        <v>1.949404761904762</v>
       </c>
       <c r="J2" t="n">
-        <v>0.567358993902439</v>
+        <v>11.07700892857143</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5455887957317074</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>4.687189980158729</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.587797619047619</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11.07700892857143</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8.151506696428571</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.949404761904762</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.376860119047619</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.95503162202381</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>10.85080309339679</v>
+      <c r="Y2" s="2" t="n">
+        <v>4136.09977324263</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +633,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.68233194527067</v>
+        <v>4071.8820861678</v>
       </c>
       <c r="D3" t="n">
-        <v>17.11799156375048</v>
+        <v>334.2084067208426</v>
       </c>
       <c r="E3" t="n">
-        <v>14.30140065274588</v>
+        <v>279.2178222678957</v>
       </c>
       <c r="F3" t="n">
         <v>1.196945109041737</v>
@@ -572,24 +652,54 @@
         <v>0.4581105751002379</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5524961890243902</v>
+        <v>1.746651785714286</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5524961890243902</v>
+        <v>10.78683035714286</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5524961890243902</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>4.867776537698412</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.265997023809524</v>
+      </c>
+      <c r="O3" t="n">
+        <v>10.78683035714286</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.68266369047619</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.746651785714286</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.453125</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>18.98308515941225</v>
+      <c r="Y3" s="2" t="n">
+        <v>370.62213882662</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +710,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.67370612730518</v>
+        <v>4068.59410430839</v>
       </c>
       <c r="D4" t="n">
-        <v>17.69253665644948</v>
+        <v>345.4257156735375</v>
       </c>
       <c r="E4" t="n">
-        <v>14.52264617419824</v>
+        <v>283.5373776867276</v>
       </c>
       <c r="F4" t="n">
         <v>1.218272238008735</v>
@@ -619,24 +729,54 @@
         <v>0.4284941502223691</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5656440548780488</v>
+        <v>1.633184523809524</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5656440548780488</v>
+        <v>11.04352678571428</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5656440548780488</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>4.949490613553113</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.731026785714286</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11.04352678571428</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.245907738095237</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.633184523809524</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.430803571428571</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.889229910714286</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>14.81496141770991</v>
+      <c r="Y4" s="2" t="n">
+        <v>289.2444848219553</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +787,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.58239143367043</v>
+        <v>4033.786848072562</v>
       </c>
       <c r="D5" t="n">
-        <v>19.90397681259527</v>
+        <v>388.6014520554315</v>
       </c>
       <c r="E5" t="n">
-        <v>14.57387801786748</v>
+        <v>284.5376184440794</v>
       </c>
       <c r="F5" t="n">
         <v>1.365729614876227</v>
@@ -666,23 +806,53 @@
         <v>0.3356711152964001</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5417301829268293</v>
+        <v>1.595982142857143</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5445884146341463</v>
+        <v>10.63244047619048</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5431592987804879</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>5.752918956043955</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.606398809523809</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10.63244047619048</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8.388871173469388</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.595982142857143</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.331473214285714</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.677641369047619</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Y5" s="2" t="n">
         <v>1.281014878366228</v>
       </c>
     </row>
@@ -694,42 +864,72 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10.55651397977394</v>
+        <v>4023.922902494331</v>
       </c>
       <c r="D6" t="n">
-        <v>19.47923987086226</v>
+        <v>380.3089689073108</v>
       </c>
       <c r="E6" t="n">
-        <v>14.61428910057719</v>
+        <v>285.3265967255547</v>
       </c>
       <c r="F6" t="n">
         <v>1.332890004898899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3496120395559582</v>
+        <v>0.3496120395559581</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5323932926829269</v>
+        <v>1.517857142857143</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5330602134146342</v>
+        <v>10.40736607142857</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5327267530487805</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>5.400927197802198</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.968377976190476</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10.40736607142857</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8.427269345238095</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.517857142857143</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.360119047619047</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.806919642857142</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Y6" s="2" t="n">
         <v>0.3819958189212016</v>
       </c>
     </row>
@@ -741,17 +941,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.63146936347412</v>
+        <v>4052.49433106576</v>
       </c>
       <c r="D7" t="n">
-        <v>19.67089513162287</v>
+        <v>384.050809712637</v>
       </c>
       <c r="E7" t="n">
-        <v>14.61674044190384</v>
+        <v>285.3744562466939</v>
       </c>
       <c r="F7" t="n">
         <v>1.34577850717179</v>
@@ -760,24 +960,54 @@
         <v>0.3452668716778041</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5385861280487805</v>
+        <v>1.571800595238095</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5423018292682927</v>
+        <v>10.58779761904762</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5404439786585367</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>5.194568452380952</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.968377976190476</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10.58779761904762</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.647073412698411</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.571800595238095</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.015997023809524</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.892898478835979</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>2.2</v>
+      <c r="Y7" s="2" t="n">
+        <v>13.05</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1018,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.69066032123736</v>
+        <v>4075.056689342403</v>
       </c>
       <c r="D8" t="n">
-        <v>19.45455228119362</v>
+        <v>379.8269731090182</v>
       </c>
       <c r="E8" t="n">
-        <v>14.66898765796568</v>
+        <v>286.3945209412348</v>
       </c>
       <c r="F8" t="n">
         <v>1.326236870247091</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3549538683860282</v>
+        <v>0.3549538683860281</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.536204268292683</v>
+        <v>1.644345238095238</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5404916158536586</v>
+        <v>10.55245535714286</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5383479420731707</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>5.147879464285714</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.951636904761904</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10.55245535714286</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.739583333333332</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.644345238095238</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.82328869047619</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.152488425925926</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.538157393292683</v>
+      <c r="Y8" s="2" t="n">
+        <v>1.732142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1095,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10.77870315288519</v>
+        <v>4108.616780045351</v>
       </c>
       <c r="D9" t="n">
-        <v>19.59599103869461</v>
+        <v>382.588396469752</v>
       </c>
       <c r="E9" t="n">
-        <v>14.77838475820495</v>
+        <v>288.5303690887633</v>
       </c>
       <c r="F9" t="n">
         <v>1.325990042843818</v>
@@ -854,24 +1114,54 @@
         <v>0.352729604337416</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
-        <v>0.529344512195122</v>
+        <v>1.521577380952381</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5724085365853658</v>
+        <v>11.17559523809524</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5516069613821138</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>5.334449404761903</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.994791666666666</v>
+      </c>
+      <c r="O9" t="n">
+        <v>11.17559523809524</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9.716889880952381</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.521577380952381</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.367559523809524</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.143229166666667</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.5944359756097561</v>
+      <c r="Y9" s="2" t="n">
+        <v>11.60565476190476</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1172,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.87834622248662</v>
+        <v>4146.598639455782</v>
       </c>
       <c r="D10" t="n">
-        <v>19.00960979519821</v>
+        <v>371.1400007633936</v>
       </c>
       <c r="E10" t="n">
-        <v>14.83206793738575</v>
+        <v>289.5784692537217</v>
       </c>
       <c r="F10" t="n">
         <v>1.281656062758622</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3782912850447164</v>
+        <v>0.3782912850447163</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5235327743902439</v>
+        <v>1.811755952380952</v>
       </c>
       <c r="J10" t="n">
-        <v>0.551733993902439</v>
+        <v>10.7719494047619</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5376333841463414</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>4.891066778273808</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.908482142857142</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10.7719494047619</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8.933035714285714</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>11</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.811755952380952</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.68563988095238</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.053808170995671</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.5621899612550812</v>
+      <c r="Y10" s="2" t="n">
+        <v>5.443787675850315</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1249,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.98185603807258</v>
+        <v>4186.054421768707</v>
       </c>
       <c r="D11" t="n">
-        <v>18.1650386961495</v>
+        <v>354.6507554962521</v>
       </c>
       <c r="E11" t="n">
-        <v>14.872479023003</v>
+        <v>290.3674475919632</v>
       </c>
       <c r="F11" t="n">
         <v>1.221386069400667</v>
@@ -948,16 +1268,54 @@
         <v>0.4182278559623619</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5681211890243902</v>
+        <v>1.729910714285714</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5681211890243902</v>
+        <v>11.09188988095238</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5681211890243902</v>
+        <v>4.312802269345237</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.366443452380952</v>
+      </c>
+      <c r="O11" t="n">
+        <v>11.09188988095238</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8.178943452380951</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>12</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.729910714285714</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.579613095238095</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.024088541666667</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1326,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.98185603807258</v>
+        <v>4186.054421768707</v>
       </c>
       <c r="D12" t="n">
-        <v>18.1650386961495</v>
+        <v>354.6507554962521</v>
       </c>
       <c r="E12" t="n">
-        <v>14.872479023003</v>
+        <v>290.3674475919632</v>
       </c>
       <c r="F12" t="n">
         <v>1.221386069400667</v>
@@ -987,16 +1345,54 @@
         <v>0.4182278559623619</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5681211890243902</v>
+        <v>1.729910714285714</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5681211890243902</v>
+        <v>11.09188988095238</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5681211890243902</v>
+        <v>4.312802269345237</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.366443452380952</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11.09188988095238</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8.178943452380951</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>12</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.729910714285714</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.579613095238095</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.024088541666667</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>5.1</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1403,73 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.06870910172516</v>
+        <v>4219.160997732426</v>
       </c>
       <c r="D13" t="n">
-        <v>17.89746397879066</v>
+        <v>349.4266776811509</v>
       </c>
       <c r="E13" t="n">
-        <v>14.79757493879737</v>
+        <v>288.9050345193772</v>
       </c>
       <c r="F13" t="n">
         <v>1.209486287639319</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4342340186550331</v>
+        <v>0.4342340186550332</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5665015243902439</v>
+        <v>1.655505952380952</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5665015243902439</v>
+        <v>11.06026785714286</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5665015243902439</v>
+        <v>4.244326636904762</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.481770833333333</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11.06026785714286</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.672526041666666</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.655505952380952</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.022321428571428</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.101593501984127</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="n">
+        <v>6.229910714285714</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1480,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11.07822724568709</v>
+        <v>4222.789115646258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.64794087991482</v>
+        <v>364.0788457507178</v>
       </c>
       <c r="E14" t="n">
-        <v>14.95921925219094</v>
+        <v>292.0609473046802</v>
       </c>
       <c r="F14" t="n">
         <v>1.24658517035798</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4003302116902847</v>
+        <v>0.4003302116902849</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.524390243902439</v>
+        <v>1.644345238095238</v>
       </c>
       <c r="J14" t="n">
-        <v>0.606516768292683</v>
+        <v>11.84151785714286</v>
       </c>
       <c r="K14" t="n">
-        <v>0.565453506097561</v>
+        <v>4.51078869047619</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.243675595238095</v>
+      </c>
+      <c r="O14" t="n">
+        <v>11.84151785714286</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8.166294642857142</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>11</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.644345238095238</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.897693452380953</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.849195075757575</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="n">
+        <v>11.60565476190476</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1557,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.07911957168352</v>
+        <v>4223.12925170068</v>
       </c>
       <c r="D15" t="n">
-        <v>19.52353827837037</v>
+        <v>381.1738425777072</v>
       </c>
       <c r="E15" t="n">
-        <v>14.97350672977727</v>
+        <v>292.3398932956514</v>
       </c>
       <c r="F15" t="n">
         <v>1.303872141022558</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3652565872717373</v>
+        <v>0.3652565872717372</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5262957317073171</v>
+        <v>1.549479166666667</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6234756097560976</v>
+        <v>12.17261904761905</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5748856707317074</v>
+        <v>4.776387117346938</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.01376488095238</v>
+      </c>
+      <c r="O15" t="n">
+        <v>12.17261904761905</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8.719122023809522</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.549479166666667</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.923735119047619</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.585978835978836</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="n">
+        <v>8.897280240221088</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1634,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.9940511600238</v>
+        <v>4190.702947845804</v>
       </c>
       <c r="D16" t="n">
-        <v>18.26505101599345</v>
+        <v>356.6033769789196</v>
       </c>
       <c r="E16" t="n">
-        <v>15.07351904380612</v>
+        <v>294.2925146647862</v>
       </c>
       <c r="F16" t="n">
         <v>1.211731047203523</v>
@@ -1143,16 +1653,54 @@
         <v>0.4141196501687838</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5240091463414634</v>
+        <v>1.716889880952381</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6252858231707318</v>
+        <v>12.20796130952381</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5746474847560976</v>
+        <v>5.788504464285714</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.265997023809524</v>
+      </c>
+      <c r="O16" t="n">
+        <v>12.20796130952381</v>
+      </c>
+      <c r="P16" t="n">
+        <v>7.621527777777778</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.716889880952381</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.827008928571428</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.038969494047619</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="n">
+        <v>7.95</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1711,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11.01576442593694</v>
+        <v>4198.979591836734</v>
       </c>
       <c r="D17" t="n">
-        <v>19.20473179293842</v>
+        <v>374.9495254811786</v>
       </c>
       <c r="E17" t="n">
-        <v>15.03065663139995</v>
+        <v>293.455677089237</v>
       </c>
       <c r="F17" t="n">
         <v>1.277704112594694</v>
@@ -1182,16 +1730,54 @@
         <v>0.3753254476477978</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>0.524485518292683</v>
+        <v>1.551339285714286</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6276676829268293</v>
+        <v>12.25446428571428</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5742822662601625</v>
+        <v>6.611793154761905</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.221354166666666</v>
+      </c>
+      <c r="O17" t="n">
+        <v>12.25446428571428</v>
+      </c>
+      <c r="P17" t="n">
+        <v>9.27641369047619</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.551339285714286</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.241071428571428</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.614862351190476</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v>1.732142857142857</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1788,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.01903628792386</v>
+        <v>4200.226757369614</v>
       </c>
       <c r="D18" t="n">
-        <v>19.24615818698232</v>
+        <v>375.75832650775</v>
       </c>
       <c r="E18" t="n">
-        <v>15.12923294160424</v>
+        <v>295.3802621932257</v>
       </c>
       <c r="F18" t="n">
         <v>1.272117248856473</v>
@@ -1221,16 +1807,54 @@
         <v>0.3738224463981239</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5248666158536586</v>
+        <v>1.724330357142857</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6134717987804879</v>
+        <v>11.97730654761905</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5663427337398375</v>
+        <v>6.130783279220779</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.00297619047619</v>
+      </c>
+      <c r="O18" t="n">
+        <v>11.97730654761905</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10.30096726190476</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.724330357142857</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.952752976190476</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.65562996031746</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="n">
+        <v>4.515718005952381</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +1865,73 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.99315883402737</v>
+        <v>4190.362811791383</v>
       </c>
       <c r="D19" t="n">
-        <v>19.5008814044115</v>
+        <v>380.7314940861293</v>
       </c>
       <c r="E19" t="n">
-        <v>15.20067031209062</v>
+        <v>296.7749918074835</v>
       </c>
       <c r="F19" t="n">
         <v>1.282896148921834</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3632652746553156</v>
+        <v>0.3632652746553155</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.546875</v>
+        <v>1.545758928571428</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5926067073170732</v>
+        <v>11.56994047619048</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5592368521341463</v>
+        <v>6.398302218614718</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8.949032738095237</v>
+      </c>
+      <c r="O19" t="n">
+        <v>11.56994047619048</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10.52455357142857</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.545758928571428</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.311755952380953</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.959759424603174</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="n">
+        <v>2.966620328094938</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +1942,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.84830458060678</v>
+        <v>4135.147392290249</v>
       </c>
       <c r="D20" t="n">
-        <v>20.99735307693481</v>
+        <v>409.9483219782511</v>
       </c>
       <c r="E20" t="n">
-        <v>15.14597178087002</v>
+        <v>295.7070681027004</v>
       </c>
       <c r="F20" t="n">
         <v>1.386332510103797</v>
@@ -1299,16 +1961,54 @@
         <v>0.3092022403214825</v>
       </c>
       <c r="H20" t="n">
+        <v>9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.40141369047619</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14.90513392857143</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.781498015873014</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.351934523809524</v>
+      </c>
+      <c r="O20" t="n">
+        <v>14.90513392857143</v>
+      </c>
+      <c r="P20" t="n">
+        <v>11.18675595238095</v>
+      </c>
+      <c r="Q20" t="n">
         <v>4</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.5228658536585366</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.7634336890243902</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.6092797256097561</v>
+      <c r="R20" t="n">
+        <v>2.40141369047619</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.066964285714286</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.524925595238095</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2019,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.84830458060678</v>
+        <v>4135.147392290249</v>
       </c>
       <c r="D21" t="n">
-        <v>20.99735307693481</v>
+        <v>409.9483219782511</v>
       </c>
       <c r="E21" t="n">
-        <v>15.14597178087002</v>
+        <v>295.7070681027004</v>
       </c>
       <c r="F21" t="n">
         <v>1.386332510103797</v>
@@ -1338,16 +2038,46 @@
         <v>0.3092022403214825</v>
       </c>
       <c r="H21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.40141369047619</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14.90513392857143</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.781498015873014</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.351934523809524</v>
+      </c>
+      <c r="O21" t="n">
+        <v>14.90513392857143</v>
+      </c>
+      <c r="P21" t="n">
+        <v>11.18675595238095</v>
+      </c>
+      <c r="Q21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.5228658536585366</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.7634336890243902</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.6092797256097561</v>
+      <c r="R21" t="n">
+        <v>2.40141369047619</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.066964285714286</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.524925595238095</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2087,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1380,6 +2110,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/38/Filled_2D_sections/sagittal/week38_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/38/Filled_2D_sections/sagittal/week38_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2147,4 +2328,1265 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week38_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4136.09977324263</v>
+      </c>
+      <c r="D10" t="n">
+        <v>69.26120901844523</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4023.922902494331</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4223.12925170068</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>370.6221388266201</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21.33814693782566</v>
+      </c>
+      <c r="E11" t="n">
+        <v>334.2084067208426</v>
+      </c>
+      <c r="F11" t="n">
+        <v>409.9483219782511</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.281014878366228</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.063091453759529</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.196945109041737</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.386332510103797</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3819958189212017</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04447172220808569</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3092022403214825</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4581105751002379</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>11</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>16</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>12</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>12</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>11</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>11</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>11</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.459674775249769</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.7880689256524122</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.818640956579121</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>102</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8.90486402894491</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.084915713563436</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.951636904761904</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14.90513392857143</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>159</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.961134040880503</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7518607293130211</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.517857142857143</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.066964285714286</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>